--- a/docentes/Torres Sánchez José Luis - Estadisticos 20241.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Mat</t>
   </si>
@@ -68,66 +68,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ERICK ANGEL</t>
-  </si>
-  <si>
-    <t>OMAR DAVID</t>
-  </si>
-  <si>
-    <t>JUAN SEBASTIAN</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOEL MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -619,16 +559,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -642,16 +585,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +662,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -733,16 +679,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>41.67</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -752,7 +698,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -782,167 +728,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920003</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920005</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920008</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920014</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920021</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920020</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920024</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Torres Sánchez José Luis - Estadisticos 20241.xlsx
+++ b/docentes/Torres Sánchez José Luis - Estadisticos 20241.xlsx
@@ -662,7 +662,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
